--- a/CetralesSEIN.xlsx
+++ b/CetralesSEIN.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\Osi-2026II\Reportes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B5FBD62-E6F1-4E85-9DDB-A965A7DFD32D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAFEB65C-4112-4CBD-9760-550867D71C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{70239AFB-455F-47D1-9241-FC92C5C59D31}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$I$177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja2!$A$1:$E$309</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2494" uniqueCount="481">
   <si>
     <t>SUR</t>
   </si>
@@ -849,9 +851,6 @@
     <t>DIESEL/RESIDUAL</t>
   </si>
   <si>
-    <t>DUAL (GAS/DIESEL</t>
-  </si>
-  <si>
     <t>RESERVA FRÍA</t>
   </si>
   <si>
@@ -1009,13 +1008,487 @@
   </si>
   <si>
     <t>PLOMO</t>
+  </si>
+  <si>
+    <t>UBICACIÓN</t>
+  </si>
+  <si>
+    <t>TIPO EQUIPO</t>
+  </si>
+  <si>
+    <t>EQUIPO</t>
+  </si>
+  <si>
+    <t>POTENCIA</t>
+  </si>
+  <si>
+    <t>CENTRAL TERMOELÉCTRICA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRAL        </t>
+  </si>
+  <si>
+    <t>GENERADOR TERMOELÉCTRICO</t>
+  </si>
+  <si>
+    <t>TV-01</t>
+  </si>
+  <si>
+    <t>MAPLE ETANOL</t>
+  </si>
+  <si>
+    <t>CENTRAL</t>
+  </si>
+  <si>
+    <t>SAN JACINTO</t>
+  </si>
+  <si>
+    <t>TV1</t>
+  </si>
+  <si>
+    <t>TV2</t>
+  </si>
+  <si>
+    <t>CENTRAL HIDROELÉCTRICA</t>
+  </si>
+  <si>
+    <t>CH HUALLIN</t>
+  </si>
+  <si>
+    <t>GENERADOR HIDROELÉCTRICO</t>
+  </si>
+  <si>
+    <t>G1</t>
+  </si>
+  <si>
+    <t>G2</t>
+  </si>
+  <si>
+    <t>EL PLATANAL</t>
+  </si>
+  <si>
+    <t>G3</t>
+  </si>
+  <si>
+    <t>CENTRAL SOLAR</t>
+  </si>
+  <si>
+    <t>GENERADOR SOLAR</t>
+  </si>
+  <si>
+    <t>G.S. COENERGY</t>
+  </si>
+  <si>
+    <t>CENTRAL SOLAR YARUCAYA</t>
+  </si>
+  <si>
+    <t>CHARCANI I</t>
+  </si>
+  <si>
+    <t>CHARCANI II</t>
+  </si>
+  <si>
+    <t>CHARCANI III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHILINA D                                         </t>
+  </si>
+  <si>
+    <t>SLZ1</t>
+  </si>
+  <si>
+    <t>SLZ2</t>
+  </si>
+  <si>
+    <t>TG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOLLENDO D                                        </t>
+  </si>
+  <si>
+    <t>GD1</t>
+  </si>
+  <si>
+    <t>GD2</t>
+  </si>
+  <si>
+    <t>GD3</t>
+  </si>
+  <si>
+    <t>RUNATULLO II</t>
+  </si>
+  <si>
+    <t>SANTA CRUZ I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRAL                  </t>
+  </si>
+  <si>
+    <t>SANTA CRUZ II</t>
+  </si>
+  <si>
+    <t>G4</t>
+  </si>
+  <si>
+    <t>ARICOTA I</t>
+  </si>
+  <si>
+    <t>ARICOTA II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDEP_G1       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDEP_G2       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDEP_G3       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">INDEP_G4       </t>
+  </si>
+  <si>
+    <t>G5</t>
+  </si>
+  <si>
+    <t>G6</t>
+  </si>
+  <si>
+    <t>G7</t>
+  </si>
+  <si>
+    <t>RESTITUCIÓN</t>
+  </si>
+  <si>
+    <t>TUMBES</t>
+  </si>
+  <si>
+    <t>MAK1</t>
+  </si>
+  <si>
+    <t>MAK2</t>
+  </si>
+  <si>
+    <t>G01</t>
+  </si>
+  <si>
+    <t>G02</t>
+  </si>
+  <si>
+    <t>RENOVANDES H1</t>
+  </si>
+  <si>
+    <t>PCH CHAGLLA</t>
+  </si>
+  <si>
+    <t>GP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMPRESA DE GENERACION HUANZA                      </t>
+  </si>
+  <si>
+    <t>1GER</t>
+  </si>
+  <si>
+    <t>2GER</t>
+  </si>
+  <si>
+    <t>MALACAS</t>
+  </si>
+  <si>
+    <t>TG4</t>
+  </si>
+  <si>
+    <t>MALACAS 1</t>
+  </si>
+  <si>
+    <t>TG6</t>
+  </si>
+  <si>
+    <t>RESERVA FRIA DE GENERACION TALARA</t>
+  </si>
+  <si>
+    <t>TG5</t>
+  </si>
+  <si>
+    <t>PARQUE EOLICO TALARA</t>
+  </si>
+  <si>
+    <t>CENTRAL EOLICA</t>
+  </si>
+  <si>
+    <t>CHILCA 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG1            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TG2            </t>
+  </si>
+  <si>
+    <t>TG3</t>
+  </si>
+  <si>
+    <t>TV</t>
+  </si>
+  <si>
+    <t>CHILCA 2</t>
+  </si>
+  <si>
+    <t>TG41</t>
+  </si>
+  <si>
+    <t>TV42</t>
+  </si>
+  <si>
+    <t>ILO 4</t>
+  </si>
+  <si>
+    <t>TG42</t>
+  </si>
+  <si>
+    <t>TG43</t>
+  </si>
+  <si>
+    <t>PUNTA LOMITAS</t>
+  </si>
+  <si>
+    <t>GENERADOR EOLICO</t>
+  </si>
+  <si>
+    <t>PL-BL1</t>
+  </si>
+  <si>
+    <t>PUNTA LOMITAS EXP</t>
+  </si>
+  <si>
+    <t>PUN LOM_EXP-BL1</t>
+  </si>
+  <si>
+    <t>RESERVA FRIA PLANTA ILO</t>
+  </si>
+  <si>
+    <t>YUNCÁN</t>
+  </si>
+  <si>
+    <t>FENIX</t>
+  </si>
+  <si>
+    <t>GT12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRAL EOLICA HUAMBOS                                                                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CENTRAL EOLICA DUNA                                                                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">G1             </t>
+  </si>
+  <si>
+    <t>RESERVA FRIA PTO MALDONADO</t>
+  </si>
+  <si>
+    <t>G1-G11</t>
+  </si>
+  <si>
+    <t>RESERVA FRIA PUCALLPA</t>
+  </si>
+  <si>
+    <t>G1-G25</t>
+  </si>
+  <si>
+    <t>SANTA TERESA</t>
+  </si>
+  <si>
+    <t>CH2 - G2</t>
+  </si>
+  <si>
+    <t>CH3 - G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CH3 - G2       </t>
+  </si>
+  <si>
+    <t>KALLPA</t>
+  </si>
+  <si>
+    <t>LAS FLORES</t>
+  </si>
+  <si>
+    <t>TG1</t>
+  </si>
+  <si>
+    <t>MINI CENTRAL CERRO DEL AGUILA</t>
+  </si>
+  <si>
+    <t>SUNNY EXPANSIÓN</t>
+  </si>
+  <si>
+    <t>CENTRAL SOLAR CARHUAQUERO</t>
+  </si>
+  <si>
+    <t>GE.U2</t>
+  </si>
+  <si>
+    <t>GE.U3</t>
+  </si>
+  <si>
+    <t>MAJES SOLAR 20T</t>
+  </si>
+  <si>
+    <t>CAÑÓN DEL PATO</t>
+  </si>
+  <si>
+    <t>CENTRAL EOLICA WAYRA I</t>
+  </si>
+  <si>
+    <t>G.E. WAYRA I</t>
+  </si>
+  <si>
+    <t>CH HER 1</t>
+  </si>
+  <si>
+    <t>HUAMPANÍ</t>
+  </si>
+  <si>
+    <t>SANTA ROSA</t>
+  </si>
+  <si>
+    <t>TG7</t>
+  </si>
+  <si>
+    <t>UTI5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UTI6           </t>
+  </si>
+  <si>
+    <t>SANTA ROSA II</t>
+  </si>
+  <si>
+    <t>TG8</t>
+  </si>
+  <si>
+    <t>VENTANILLA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TV             </t>
+  </si>
+  <si>
+    <t>PARQUE EOLICO MARCONA</t>
+  </si>
+  <si>
+    <t>PARQUE EOLICO 3 HERMANAS</t>
+  </si>
+  <si>
+    <t>CTB CALLAO</t>
+  </si>
+  <si>
+    <t>G1 CALLAO</t>
+  </si>
+  <si>
+    <t>G2 CALLAO</t>
+  </si>
+  <si>
+    <t>DOÑA CATALINA</t>
+  </si>
+  <si>
+    <t>LA GRINGA V</t>
+  </si>
+  <si>
+    <t>RESERVA FRIA DE GENERACION ETEN</t>
+  </si>
+  <si>
+    <t>RF-ETENGT1</t>
+  </si>
+  <si>
+    <t>RF-ETENGT2</t>
+  </si>
+  <si>
+    <t>REPARTICION SOLAR 20T</t>
+  </si>
+  <si>
+    <t>PUERTO BRAVO</t>
+  </si>
+  <si>
+    <t>TG2</t>
+  </si>
+  <si>
+    <t>PCH TUPURI</t>
+  </si>
+  <si>
+    <t>SAN GABÁN II</t>
+  </si>
+  <si>
+    <t>SAN NICOLÁS</t>
+  </si>
+  <si>
+    <t>TV3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SINERSA                                           </t>
+  </si>
+  <si>
+    <t>GH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GALLITO CIEGO                                     </t>
+  </si>
+  <si>
+    <t>SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>SAN IGNACIO</t>
+  </si>
+  <si>
+    <t>SANTO DOMINGO DE LOS OLLEROS</t>
+  </si>
+  <si>
+    <t>AGUAYTÍA</t>
+  </si>
+  <si>
+    <t>CENTRAL SOLAR RUBI</t>
+  </si>
+  <si>
+    <t>CENTRAL SOLAR CLEMESI</t>
+  </si>
+  <si>
+    <t>CS_CLEMESI</t>
+  </si>
+  <si>
+    <t>RUNATULLO III</t>
+  </si>
+  <si>
+    <t>HUASAHUASI II</t>
+  </si>
+  <si>
+    <t>HUASAHUASI I</t>
+  </si>
+  <si>
+    <t>CA?A BRAVA</t>
+  </si>
+  <si>
+    <t>CARHUAQUERO IV</t>
+  </si>
+  <si>
+    <t>GT11</t>
+  </si>
+  <si>
+    <t>TV10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G2            </t>
+  </si>
+  <si>
+    <t>DUAL (GAS/DIESEL)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1038,16 +1511,62 @@
       <sz val="8"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
+      <name val="Muli"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color indexed="64"/>
+      <name val="Microsoft Sans Serif"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17375D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1081,11 +1600,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1095,6 +1634,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1410,7 +1962,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A457A5FF-58BA-4FEE-9EE7-1F24D64D05BC}">
   <dimension ref="A1:FT360"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="40.5703125" style="1" customWidth="1"/>
@@ -1424,15 +1976,15 @@
     <col min="10" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:176">
       <c r="A1" s="3" t="s">
         <v>261</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>264</v>
@@ -1441,7 +1993,7 @@
         <v>262</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>265</v>
@@ -1450,7 +2002,7 @@
         <v>263</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="FM1" s="2" t="s">
         <v>260</v>
@@ -1477,7 +2029,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="2" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:176">
       <c r="A2" s="3">
         <v>59715</v>
       </c>
@@ -1502,7 +2054,7 @@
       </c>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:176">
       <c r="A3" s="3">
         <v>1263</v>
       </c>
@@ -1527,7 +2079,7 @@
       </c>
       <c r="I3" s="3"/>
     </row>
-    <row r="4" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:176">
       <c r="A4" s="3">
         <v>253</v>
       </c>
@@ -1552,7 +2104,7 @@
       </c>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:176">
       <c r="A5" s="3">
         <v>770</v>
       </c>
@@ -1577,7 +2129,7 @@
       </c>
       <c r="I5" s="3"/>
     </row>
-    <row r="6" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:176">
       <c r="A6" s="3">
         <v>257</v>
       </c>
@@ -1602,7 +2154,7 @@
       </c>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:176">
       <c r="A7" s="3">
         <v>256</v>
       </c>
@@ -1627,7 +2179,7 @@
       </c>
       <c r="I7" s="3"/>
     </row>
-    <row r="8" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:176">
       <c r="A8" s="3">
         <v>58288</v>
       </c>
@@ -1652,7 +2204,7 @@
       </c>
       <c r="I8" s="3"/>
     </row>
-    <row r="9" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:176">
       <c r="A9" s="3">
         <v>58289</v>
       </c>
@@ -1677,7 +2229,7 @@
       </c>
       <c r="I9" s="3"/>
     </row>
-    <row r="10" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:176">
       <c r="A10" s="3">
         <v>58839</v>
       </c>
@@ -1702,7 +2254,7 @@
       </c>
       <c r="I10" s="3"/>
     </row>
-    <row r="11" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:176">
       <c r="A11" s="3">
         <v>58840</v>
       </c>
@@ -1727,7 +2279,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:176">
       <c r="A12" s="3">
         <v>1262</v>
       </c>
@@ -1752,7 +2304,7 @@
       </c>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:176">
       <c r="A13" s="3">
         <v>2161</v>
       </c>
@@ -1777,7 +2329,7 @@
       </c>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:176">
       <c r="A14" s="3">
         <v>61197</v>
       </c>
@@ -1802,7 +2354,7 @@
       </c>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:176">
       <c r="A15" s="3">
         <v>65333</v>
       </c>
@@ -1827,7 +2379,7 @@
       </c>
       <c r="I15" s="3"/>
     </row>
-    <row r="16" spans="1:176" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:176">
       <c r="A16" s="3">
         <v>101</v>
       </c>
@@ -1852,7 +2404,7 @@
       </c>
       <c r="I16" s="3"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9">
       <c r="A17" s="3">
         <v>102</v>
       </c>
@@ -1877,7 +2429,7 @@
       </c>
       <c r="I17" s="3"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9">
       <c r="A18" s="3">
         <v>126</v>
       </c>
@@ -1902,7 +2454,7 @@
       </c>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9">
       <c r="A19" s="3">
         <v>127</v>
       </c>
@@ -1927,7 +2479,7 @@
       </c>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9">
       <c r="A20" s="3">
         <v>796</v>
       </c>
@@ -1952,7 +2504,7 @@
       </c>
       <c r="I20" s="3"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9">
       <c r="A21" s="3">
         <v>2146</v>
       </c>
@@ -1977,7 +2529,7 @@
       </c>
       <c r="I21" s="3"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9">
       <c r="A22" s="3">
         <v>163</v>
       </c>
@@ -2002,7 +2554,7 @@
       </c>
       <c r="I22" s="3"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9">
       <c r="A23" s="3">
         <v>298</v>
       </c>
@@ -2027,7 +2579,7 @@
       </c>
       <c r="I23" s="3"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9">
       <c r="A24" s="3">
         <v>299</v>
       </c>
@@ -2052,7 +2604,7 @@
       </c>
       <c r="I24" s="3"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9">
       <c r="A25" s="3">
         <v>151</v>
       </c>
@@ -2077,7 +2629,7 @@
       </c>
       <c r="I25" s="3"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9">
       <c r="A26" s="3">
         <v>152</v>
       </c>
@@ -2102,7 +2654,7 @@
       </c>
       <c r="I26" s="3"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9">
       <c r="A27" s="3">
         <v>153</v>
       </c>
@@ -2127,7 +2679,7 @@
       </c>
       <c r="I27" s="3"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9">
       <c r="A28" s="3">
         <v>154</v>
       </c>
@@ -2152,7 +2704,7 @@
       </c>
       <c r="I28" s="3"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9">
       <c r="A29" s="3">
         <v>182</v>
       </c>
@@ -2177,7 +2729,7 @@
       </c>
       <c r="I29" s="3"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9">
       <c r="A30" s="3">
         <v>212</v>
       </c>
@@ -2202,7 +2754,7 @@
       </c>
       <c r="I30" s="3"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9">
       <c r="A31" s="3">
         <v>775</v>
       </c>
@@ -2227,7 +2779,7 @@
       </c>
       <c r="I31" s="3"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9">
       <c r="A32" s="3">
         <v>777</v>
       </c>
@@ -2252,7 +2804,7 @@
       </c>
       <c r="I32" s="3"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9">
       <c r="A33" s="3">
         <v>2154</v>
       </c>
@@ -2277,7 +2829,7 @@
       </c>
       <c r="I33" s="3"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9">
       <c r="A34" s="3">
         <v>150</v>
       </c>
@@ -2302,7 +2854,7 @@
       </c>
       <c r="I34" s="3"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9">
       <c r="A35" s="3">
         <v>149</v>
       </c>
@@ -2327,7 +2879,7 @@
       </c>
       <c r="I35" s="3"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9">
       <c r="A36" s="3">
         <v>188</v>
       </c>
@@ -2352,7 +2904,7 @@
       </c>
       <c r="I36" s="3"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9">
       <c r="A37" s="3">
         <v>2131</v>
       </c>
@@ -2377,7 +2929,7 @@
       </c>
       <c r="I37" s="3"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9">
       <c r="A38" s="3">
         <v>755</v>
       </c>
@@ -2402,7 +2954,7 @@
       </c>
       <c r="I38" s="3"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9">
       <c r="A39" s="3">
         <v>117</v>
       </c>
@@ -2427,7 +2979,7 @@
       </c>
       <c r="I39" s="3"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9">
       <c r="A40" s="3">
         <v>119</v>
       </c>
@@ -2452,7 +3004,7 @@
       </c>
       <c r="I40" s="3"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9">
       <c r="A41" s="3">
         <v>120</v>
       </c>
@@ -2477,7 +3029,7 @@
       </c>
       <c r="I41" s="3"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9">
       <c r="A42" s="3">
         <v>189</v>
       </c>
@@ -2502,7 +3054,7 @@
       </c>
       <c r="I42" s="3"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9">
       <c r="A43" s="3">
         <v>122</v>
       </c>
@@ -2527,7 +3079,7 @@
       </c>
       <c r="I43" s="3"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9">
       <c r="A44" s="3">
         <v>266</v>
       </c>
@@ -2552,7 +3104,7 @@
       </c>
       <c r="I44" s="3"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9">
       <c r="A45" s="3">
         <v>337</v>
       </c>
@@ -2577,7 +3129,7 @@
       </c>
       <c r="I45" s="3"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9">
       <c r="A46" s="3">
         <v>338</v>
       </c>
@@ -2602,7 +3154,7 @@
       </c>
       <c r="I46" s="3"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9">
       <c r="A47" s="3">
         <v>251</v>
       </c>
@@ -2627,7 +3179,7 @@
       </c>
       <c r="I47" s="3"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9">
       <c r="A48" s="3">
         <v>191</v>
       </c>
@@ -2652,7 +3204,7 @@
       </c>
       <c r="I48" s="3"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9">
       <c r="A49" s="3">
         <v>766</v>
       </c>
@@ -2677,7 +3229,7 @@
       </c>
       <c r="I49" s="3"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9">
       <c r="A50" s="3">
         <v>121</v>
       </c>
@@ -2702,7 +3254,7 @@
       </c>
       <c r="I50" s="3"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9">
       <c r="A51" s="3">
         <v>103</v>
       </c>
@@ -2727,7 +3279,7 @@
       </c>
       <c r="I51" s="3"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9">
       <c r="A52" s="3">
         <v>104</v>
       </c>
@@ -2752,7 +3304,7 @@
       </c>
       <c r="I52" s="3"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9">
       <c r="A53" s="3">
         <v>106</v>
       </c>
@@ -2777,7 +3329,7 @@
       </c>
       <c r="I53" s="3"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9">
       <c r="A54" s="3">
         <v>105</v>
       </c>
@@ -2802,7 +3354,7 @@
       </c>
       <c r="I54" s="3"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9">
       <c r="A55" s="3">
         <v>107</v>
       </c>
@@ -2827,7 +3379,7 @@
       </c>
       <c r="I55" s="3"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9">
       <c r="A56" s="3">
         <v>267</v>
       </c>
@@ -2852,7 +3404,7 @@
       </c>
       <c r="I56" s="3"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9">
       <c r="A57" s="3">
         <v>268</v>
       </c>
@@ -2877,7 +3429,7 @@
       </c>
       <c r="I57" s="3"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9">
       <c r="A58" s="3">
         <v>2194</v>
       </c>
@@ -2902,7 +3454,7 @@
       </c>
       <c r="I58" s="3"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9">
       <c r="A59" s="3">
         <v>69125</v>
       </c>
@@ -2927,7 +3479,7 @@
       </c>
       <c r="I59" s="3"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9">
       <c r="A60" s="3">
         <v>216</v>
       </c>
@@ -2952,7 +3504,7 @@
       </c>
       <c r="I60" s="3"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9">
       <c r="A61" s="3">
         <v>198</v>
       </c>
@@ -2977,7 +3529,7 @@
       </c>
       <c r="I61" s="3"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9">
       <c r="A62" s="3">
         <v>49607</v>
       </c>
@@ -3002,7 +3554,7 @@
       </c>
       <c r="I62" s="3"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9">
       <c r="A63" s="3">
         <v>214</v>
       </c>
@@ -3027,7 +3579,7 @@
       </c>
       <c r="I63" s="3"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9">
       <c r="A64" s="3">
         <v>260</v>
       </c>
@@ -3052,7 +3604,7 @@
       </c>
       <c r="I64" s="3"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9">
       <c r="A65" s="3">
         <v>2152</v>
       </c>
@@ -3077,7 +3629,7 @@
       </c>
       <c r="I65" s="3"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9">
       <c r="A66" s="3">
         <v>2128</v>
       </c>
@@ -3102,7 +3654,7 @@
       </c>
       <c r="I66" s="3"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9">
       <c r="A67" s="3">
         <v>247</v>
       </c>
@@ -3127,7 +3679,7 @@
       </c>
       <c r="I67" s="3"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9">
       <c r="A68" s="3">
         <v>228</v>
       </c>
@@ -3152,7 +3704,7 @@
       </c>
       <c r="I68" s="3"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9">
       <c r="A69" s="3">
         <v>2135</v>
       </c>
@@ -3177,7 +3729,7 @@
       </c>
       <c r="I69" s="3"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9">
       <c r="A70" s="3">
         <v>238</v>
       </c>
@@ -3202,7 +3754,7 @@
       </c>
       <c r="I70" s="3"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9">
       <c r="A71" s="3">
         <v>2184</v>
       </c>
@@ -3227,7 +3779,7 @@
       </c>
       <c r="I71" s="3"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9">
       <c r="A72" s="3">
         <v>61855</v>
       </c>
@@ -3252,7 +3804,7 @@
       </c>
       <c r="I72" s="3"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9">
       <c r="A73" s="3">
         <v>223</v>
       </c>
@@ -3277,7 +3829,7 @@
       </c>
       <c r="I73" s="3"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9">
       <c r="A74" s="3">
         <v>226</v>
       </c>
@@ -3302,7 +3854,7 @@
       </c>
       <c r="I74" s="3"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9">
       <c r="A75" s="3">
         <v>201</v>
       </c>
@@ -3327,7 +3879,7 @@
       </c>
       <c r="I75" s="3"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9">
       <c r="A76" s="3">
         <v>258</v>
       </c>
@@ -3352,7 +3904,7 @@
       </c>
       <c r="I76" s="3"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9">
       <c r="A77" s="3">
         <v>259</v>
       </c>
@@ -3377,7 +3929,7 @@
       </c>
       <c r="I77" s="3"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9">
       <c r="A78" s="3">
         <v>296</v>
       </c>
@@ -3402,7 +3954,7 @@
       </c>
       <c r="I78" s="3"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9">
       <c r="A79" s="3">
         <v>297</v>
       </c>
@@ -3427,7 +3979,7 @@
       </c>
       <c r="I79" s="3"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9">
       <c r="A80" s="3">
         <v>211</v>
       </c>
@@ -3452,7 +4004,7 @@
       </c>
       <c r="I80" s="3"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9">
       <c r="A81" s="3">
         <v>2175</v>
       </c>
@@ -3477,7 +4029,7 @@
       </c>
       <c r="I81" s="3"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9">
       <c r="A82" s="3">
         <v>2178</v>
       </c>
@@ -3502,7 +4054,7 @@
       </c>
       <c r="I82" s="3"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9">
       <c r="A83" s="3">
         <v>2181</v>
       </c>
@@ -3527,7 +4079,7 @@
       </c>
       <c r="I83" s="3"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9">
       <c r="A84" s="3">
         <v>2165</v>
       </c>
@@ -3552,7 +4104,7 @@
       </c>
       <c r="I84" s="3"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9">
       <c r="A85" s="3">
         <v>215</v>
       </c>
@@ -3577,7 +4129,7 @@
       </c>
       <c r="I85" s="3"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9">
       <c r="A86" s="3">
         <v>917</v>
       </c>
@@ -3602,7 +4154,7 @@
       </c>
       <c r="I86" s="3"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9">
       <c r="A87" s="3">
         <v>920</v>
       </c>
@@ -3627,7 +4179,7 @@
       </c>
       <c r="I87" s="3"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9">
       <c r="A88" s="3">
         <v>221</v>
       </c>
@@ -3652,7 +4204,7 @@
       </c>
       <c r="I88" s="3"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9">
       <c r="A89" s="3">
         <v>222</v>
       </c>
@@ -3677,7 +4229,7 @@
       </c>
       <c r="I89" s="3"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9">
       <c r="A90" s="3">
         <v>224</v>
       </c>
@@ -3702,7 +4254,7 @@
       </c>
       <c r="I90" s="3"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9">
       <c r="A91" s="3">
         <v>2187</v>
       </c>
@@ -3727,7 +4279,7 @@
       </c>
       <c r="I91" s="3"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9">
       <c r="A92" s="3">
         <v>199</v>
       </c>
@@ -3752,7 +4304,7 @@
       </c>
       <c r="I92" s="3"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9">
       <c r="A93" s="3">
         <v>200</v>
       </c>
@@ -3777,7 +4329,7 @@
       </c>
       <c r="I93" s="3"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9">
       <c r="A94" s="3">
         <v>303</v>
       </c>
@@ -3802,7 +4354,7 @@
       </c>
       <c r="I94" s="3"/>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9">
       <c r="A95" s="3">
         <v>62255</v>
       </c>
@@ -3827,7 +4379,7 @@
       </c>
       <c r="I95" s="3"/>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9">
       <c r="A96" s="3">
         <v>61800</v>
       </c>
@@ -3852,7 +4404,7 @@
       </c>
       <c r="I96" s="3"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9">
       <c r="A97" s="3">
         <v>70400</v>
       </c>
@@ -3877,7 +4429,7 @@
       </c>
       <c r="I97" s="3"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9">
       <c r="A98" s="3">
         <v>76068</v>
       </c>
@@ -3902,7 +4454,7 @@
       </c>
       <c r="I98" s="3"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9">
       <c r="A99" s="3">
         <v>261</v>
       </c>
@@ -3927,7 +4479,7 @@
       </c>
       <c r="I99" s="3"/>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9">
       <c r="A100" s="3">
         <v>237</v>
       </c>
@@ -3952,7 +4504,7 @@
       </c>
       <c r="I100" s="3"/>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9">
       <c r="A101" s="3">
         <v>235</v>
       </c>
@@ -3977,7 +4529,7 @@
       </c>
       <c r="I101" s="3"/>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9">
       <c r="A102" s="3">
         <v>75566</v>
       </c>
@@ -4002,7 +4554,7 @@
       </c>
       <c r="I102" s="3"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9">
       <c r="A103" s="3">
         <v>2148</v>
       </c>
@@ -4027,7 +4579,7 @@
       </c>
       <c r="I103" s="3"/>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9">
       <c r="A104" s="3">
         <v>75260</v>
       </c>
@@ -4052,7 +4604,7 @@
       </c>
       <c r="I104" s="3"/>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9">
       <c r="A105" s="3">
         <v>63425</v>
       </c>
@@ -4077,7 +4629,7 @@
       </c>
       <c r="I105" s="3"/>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9">
       <c r="A106" s="3">
         <v>233</v>
       </c>
@@ -4102,7 +4654,7 @@
       </c>
       <c r="I106" s="3"/>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9">
       <c r="A107" s="3">
         <v>2150</v>
       </c>
@@ -4127,7 +4679,7 @@
       </c>
       <c r="I107" s="3"/>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9">
       <c r="A108" s="3">
         <v>58851</v>
       </c>
@@ -4152,7 +4704,7 @@
       </c>
       <c r="I108" s="3"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9">
       <c r="A109" s="3">
         <v>234</v>
       </c>
@@ -4177,7 +4729,7 @@
       </c>
       <c r="I109" s="3"/>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9">
       <c r="A110" s="3">
         <v>42667</v>
       </c>
@@ -4185,7 +4737,7 @@
         <v>88</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>8</v>
@@ -4204,7 +4756,7 @@
       </c>
       <c r="I110" s="3"/>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9">
       <c r="A111" s="3">
         <v>42668</v>
       </c>
@@ -4212,7 +4764,7 @@
         <v>89</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>8</v>
@@ -4231,7 +4783,7 @@
       </c>
       <c r="I111" s="3"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9">
       <c r="A112" s="3">
         <v>138</v>
       </c>
@@ -4239,7 +4791,7 @@
         <v>92</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>10</v>
@@ -4254,11 +4806,11 @@
         <v>266</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I112" s="3"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9">
       <c r="A113" s="3">
         <v>139</v>
       </c>
@@ -4266,7 +4818,7 @@
         <v>93</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>10</v>
@@ -4281,11 +4833,11 @@
         <v>266</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="I113" s="3"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9">
       <c r="A114" s="3">
         <v>197</v>
       </c>
@@ -4293,7 +4845,7 @@
         <v>94</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>11</v>
@@ -4308,11 +4860,11 @@
         <v>266</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I114" s="3"/>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9">
       <c r="A115" s="3">
         <v>203</v>
       </c>
@@ -4320,7 +4872,7 @@
         <v>95</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>11</v>
@@ -4335,11 +4887,11 @@
         <v>266</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I115" s="3"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9">
       <c r="A116" s="3">
         <v>204</v>
       </c>
@@ -4347,7 +4899,7 @@
         <v>96</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>11</v>
@@ -4362,11 +4914,11 @@
         <v>266</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I116" s="3"/>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9">
       <c r="A117" s="3">
         <v>230</v>
       </c>
@@ -4374,7 +4926,7 @@
         <v>97</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>11</v>
@@ -4389,11 +4941,11 @@
         <v>266</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I117" s="3"/>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9">
       <c r="A118" s="3">
         <v>209</v>
       </c>
@@ -4401,7 +4953,7 @@
         <v>98</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>11</v>
@@ -4416,11 +4968,11 @@
         <v>266</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I118" s="3"/>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9">
       <c r="A119" s="3">
         <v>56677</v>
       </c>
@@ -4428,7 +4980,7 @@
         <v>99</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D119" s="3" t="s">
         <v>11</v>
@@ -4443,11 +4995,11 @@
         <v>266</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I119" s="3"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9">
       <c r="A120" s="3">
         <v>142</v>
       </c>
@@ -4455,7 +5007,7 @@
         <v>102</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>12</v>
@@ -4474,7 +5026,7 @@
       </c>
       <c r="I120" s="3"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9">
       <c r="A121" s="3">
         <v>143</v>
       </c>
@@ -4482,7 +5034,7 @@
         <v>103</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>12</v>
@@ -4501,7 +5053,7 @@
       </c>
       <c r="I121" s="3"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9">
       <c r="A122" s="3">
         <v>125</v>
       </c>
@@ -4509,7 +5061,7 @@
         <v>104</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>12</v>
@@ -4528,7 +5080,7 @@
       </c>
       <c r="I122" s="3"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9">
       <c r="A123" s="3">
         <v>187</v>
       </c>
@@ -4536,7 +5088,7 @@
         <v>105</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>12</v>
@@ -4555,7 +5107,7 @@
       </c>
       <c r="I123" s="3"/>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9">
       <c r="A124" s="3">
         <v>219</v>
       </c>
@@ -4563,7 +5115,7 @@
         <v>109</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>14</v>
@@ -4578,11 +5130,11 @@
         <v>266</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I124" s="3"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9">
       <c r="A125" s="3">
         <v>756</v>
       </c>
@@ -4590,7 +5142,7 @@
         <v>114</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>15</v>
@@ -4609,7 +5161,7 @@
       </c>
       <c r="I125" s="3"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9">
       <c r="A126" s="3">
         <v>156</v>
       </c>
@@ -4617,7 +5169,7 @@
         <v>115</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>15</v>
@@ -4636,7 +5188,7 @@
       </c>
       <c r="I126" s="3"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9">
       <c r="A127" s="3">
         <v>155</v>
       </c>
@@ -4644,7 +5196,7 @@
         <v>116</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>15</v>
@@ -4663,7 +5215,7 @@
       </c>
       <c r="I127" s="3"/>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9">
       <c r="A128" s="3">
         <v>758</v>
       </c>
@@ -4671,7 +5223,7 @@
         <v>119</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>18</v>
@@ -4690,7 +5242,7 @@
       </c>
       <c r="I128" s="3"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9">
       <c r="A129" s="3">
         <v>263</v>
       </c>
@@ -4698,7 +5250,7 @@
         <v>120</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>19</v>
@@ -4716,10 +5268,10 @@
         <v>269</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
       <c r="A130" s="3">
         <v>265</v>
       </c>
@@ -4727,7 +5279,7 @@
         <v>121</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>19</v>
@@ -4745,10 +5297,10 @@
         <v>269</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
       <c r="A131" s="3">
         <v>252</v>
       </c>
@@ -4756,7 +5308,7 @@
         <v>129</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>26</v>
@@ -4771,13 +5323,13 @@
         <v>266</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
       <c r="A132" s="3">
         <v>249</v>
       </c>
@@ -4785,7 +5337,7 @@
         <v>130</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>26</v>
@@ -4800,13 +5352,13 @@
         <v>266</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
       <c r="A133" s="3">
         <v>250</v>
       </c>
@@ -4814,7 +5366,7 @@
         <v>131</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>26</v>
@@ -4829,13 +5381,13 @@
         <v>266</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
       <c r="A134" s="3">
         <v>115</v>
       </c>
@@ -4843,7 +5395,7 @@
         <v>141</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>30</v>
@@ -4858,11 +5410,11 @@
         <v>266</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I134" s="3"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9">
       <c r="A135" s="3">
         <v>239</v>
       </c>
@@ -4870,7 +5422,7 @@
         <v>142</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>30</v>
@@ -4885,13 +5437,13 @@
         <v>266</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>313</v>
+        <v>269</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9">
       <c r="A136" s="3">
         <v>288</v>
       </c>
@@ -4899,7 +5451,7 @@
         <v>143</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D136" s="3" t="s">
         <v>30</v>
@@ -4914,11 +5466,11 @@
         <v>266</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I136" s="3"/>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9">
       <c r="A137" s="3">
         <v>240</v>
       </c>
@@ -4926,7 +5478,7 @@
         <v>144</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>31</v>
@@ -4944,10 +5496,10 @@
         <v>269</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9">
       <c r="A138" s="3">
         <v>241</v>
       </c>
@@ -4955,7 +5507,7 @@
         <v>145</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>31</v>
@@ -4973,10 +5525,10 @@
         <v>269</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9">
       <c r="A139" s="3">
         <v>242</v>
       </c>
@@ -4984,7 +5536,7 @@
         <v>146</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>31</v>
@@ -5002,10 +5554,10 @@
         <v>269</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9">
       <c r="A140" s="3">
         <v>194</v>
       </c>
@@ -5013,7 +5565,7 @@
         <v>148</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D140" s="3" t="s">
         <v>31</v>
@@ -5028,11 +5580,11 @@
         <v>266</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I140" s="3"/>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9">
       <c r="A141" s="3">
         <v>196</v>
       </c>
@@ -5040,7 +5592,7 @@
         <v>149</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D141" s="3" t="s">
         <v>31</v>
@@ -5055,11 +5607,11 @@
         <v>266</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I141" s="3"/>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9">
       <c r="A142" s="3">
         <v>207</v>
       </c>
@@ -5067,7 +5619,7 @@
         <v>150</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D142" s="3" t="s">
         <v>31</v>
@@ -5082,11 +5634,11 @@
         <v>266</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I142" s="3"/>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9">
       <c r="A143" s="3">
         <v>236</v>
       </c>
@@ -5094,7 +5646,7 @@
         <v>151</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D143" s="3" t="s">
         <v>31</v>
@@ -5109,11 +5661,11 @@
         <v>266</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I143" s="3"/>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9">
       <c r="A144" s="3">
         <v>795</v>
       </c>
@@ -5121,7 +5673,7 @@
         <v>152</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D144" s="3" t="s">
         <v>31</v>
@@ -5136,11 +5688,11 @@
         <v>266</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I144" s="3"/>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9">
       <c r="A145" s="3">
         <v>285</v>
       </c>
@@ -5148,7 +5700,7 @@
         <v>153</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D145" s="3" t="s">
         <v>31</v>
@@ -5163,11 +5715,11 @@
         <v>266</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I145" s="3"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9">
       <c r="A146" s="3">
         <v>995</v>
       </c>
@@ -5175,7 +5727,7 @@
         <v>154</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D146" s="3" t="s">
         <v>31</v>
@@ -5193,10 +5745,10 @@
         <v>269</v>
       </c>
       <c r="I146" s="3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9">
       <c r="A147" s="3">
         <v>996</v>
       </c>
@@ -5204,7 +5756,7 @@
         <v>155</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D147" s="3" t="s">
         <v>31</v>
@@ -5222,10 +5774,10 @@
         <v>269</v>
       </c>
       <c r="I147" s="3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9">
       <c r="A148" s="3">
         <v>997</v>
       </c>
@@ -5233,7 +5785,7 @@
         <v>156</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D148" s="3" t="s">
         <v>31</v>
@@ -5251,10 +5803,10 @@
         <v>269</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9">
       <c r="A149" s="3">
         <v>926</v>
       </c>
@@ -5262,7 +5814,7 @@
         <v>158</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D149" s="3" t="s">
         <v>32</v>
@@ -5280,10 +5832,10 @@
         <v>269</v>
       </c>
       <c r="I149" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
       <c r="A150" s="3">
         <v>924</v>
       </c>
@@ -5291,7 +5843,7 @@
         <v>159</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D150" s="3" t="s">
         <v>32</v>
@@ -5309,10 +5861,10 @@
         <v>269</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
       <c r="A151" s="3">
         <v>110</v>
       </c>
@@ -5320,7 +5872,7 @@
         <v>166</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D151" s="3" t="s">
         <v>34</v>
@@ -5335,13 +5887,13 @@
         <v>266</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I151" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
       <c r="A152" s="3">
         <v>109</v>
       </c>
@@ -5349,7 +5901,7 @@
         <v>167</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D152" s="3" t="s">
         <v>34</v>
@@ -5364,13 +5916,13 @@
         <v>266</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
       <c r="A153" s="3">
         <v>144</v>
       </c>
@@ -5378,7 +5930,7 @@
         <v>168</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D153" s="3" t="s">
         <v>34</v>
@@ -5393,13 +5945,13 @@
         <v>266</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I153" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
       <c r="A154" s="3">
         <v>113</v>
       </c>
@@ -5407,7 +5959,7 @@
         <v>169</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D154" s="3" t="s">
         <v>34</v>
@@ -5422,13 +5974,13 @@
         <v>266</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I154" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
       <c r="A155" s="3">
         <v>114</v>
       </c>
@@ -5436,7 +5988,7 @@
         <v>170</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D155" s="3" t="s">
         <v>34</v>
@@ -5451,13 +6003,13 @@
         <v>266</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I155" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
       <c r="A156" s="3">
         <v>193</v>
       </c>
@@ -5465,7 +6017,7 @@
         <v>171</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>34</v>
@@ -5480,13 +6032,13 @@
         <v>266</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I156" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
       <c r="A157" s="3">
         <v>208</v>
       </c>
@@ -5494,7 +6046,7 @@
         <v>172</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>34</v>
@@ -5509,11 +6061,11 @@
         <v>266</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I157" s="3"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9">
       <c r="A158" s="3">
         <v>786</v>
       </c>
@@ -5521,7 +6073,7 @@
         <v>173</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D158" s="3" t="s">
         <v>35</v>
@@ -5539,10 +6091,10 @@
         <v>269</v>
       </c>
       <c r="I158" s="3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
       <c r="A159" s="3">
         <v>787</v>
       </c>
@@ -5550,7 +6102,7 @@
         <v>174</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D159" s="3" t="s">
         <v>35</v>
@@ -5568,10 +6120,10 @@
         <v>269</v>
       </c>
       <c r="I159" s="3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
       <c r="A160" s="3">
         <v>788</v>
       </c>
@@ -5579,7 +6131,7 @@
         <v>175</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>35</v>
@@ -5597,10 +6149,10 @@
         <v>269</v>
       </c>
       <c r="I160" s="3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
       <c r="A161" s="3">
         <v>789</v>
       </c>
@@ -5608,7 +6160,7 @@
         <v>176</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>35</v>
@@ -5626,10 +6178,10 @@
         <v>269</v>
       </c>
       <c r="I161" s="3" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
       <c r="A162" s="3">
         <v>248</v>
       </c>
@@ -5637,7 +6189,7 @@
         <v>177</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>36</v>
@@ -5652,11 +6204,11 @@
         <v>266</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I162" s="3"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9">
       <c r="A163" s="3">
         <v>2159</v>
       </c>
@@ -5664,7 +6216,7 @@
         <v>178</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D163" s="3" t="s">
         <v>36</v>
@@ -5679,11 +6231,11 @@
         <v>266</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I163" s="3"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9">
       <c r="A164" s="3">
         <v>225</v>
       </c>
@@ -5691,7 +6243,7 @@
         <v>236</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D164" s="3" t="s">
         <v>69</v>
@@ -5710,7 +6262,7 @@
       </c>
       <c r="I164" s="3"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9">
       <c r="A165" s="3">
         <v>2201</v>
       </c>
@@ -5718,7 +6270,7 @@
         <v>237</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D165" s="3" t="s">
         <v>69</v>
@@ -5737,7 +6289,7 @@
       </c>
       <c r="I165" s="3"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9">
       <c r="A166" s="3">
         <v>2171</v>
       </c>
@@ -5745,7 +6297,7 @@
         <v>238</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D166" s="3" t="s">
         <v>69</v>
@@ -5764,7 +6316,7 @@
       </c>
       <c r="I166" s="3"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9">
       <c r="A167" s="3">
         <v>760</v>
       </c>
@@ -5772,7 +6324,7 @@
         <v>239</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>69</v>
@@ -5791,7 +6343,7 @@
       </c>
       <c r="I167" s="3"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9">
       <c r="A168" s="3">
         <v>289</v>
       </c>
@@ -5799,7 +6351,7 @@
         <v>244</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D168" s="3" t="s">
         <v>72</v>
@@ -5818,7 +6370,7 @@
       </c>
       <c r="I168" s="3"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9">
       <c r="A169" s="3">
         <v>58333</v>
       </c>
@@ -5826,7 +6378,7 @@
         <v>245</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D169" s="3" t="s">
         <v>73</v>
@@ -5841,11 +6393,11 @@
         <v>266</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I169" s="3"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9">
       <c r="A170" s="3">
         <v>58336</v>
       </c>
@@ -5853,7 +6405,7 @@
         <v>246</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D170" s="3" t="s">
         <v>73</v>
@@ -5868,11 +6420,11 @@
         <v>266</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I170" s="3"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9">
       <c r="A171" s="3">
         <v>213</v>
       </c>
@@ -5880,7 +6432,7 @@
         <v>247</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D171" s="3" t="s">
         <v>74</v>
@@ -5899,7 +6451,7 @@
       </c>
       <c r="I171" s="3"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9">
       <c r="A172" s="3">
         <v>232</v>
       </c>
@@ -5907,7 +6459,7 @@
         <v>248</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D172" s="3" t="s">
         <v>75</v>
@@ -5926,7 +6478,7 @@
       </c>
       <c r="I172" s="3"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9">
       <c r="A173" s="3">
         <v>2190</v>
       </c>
@@ -5934,7 +6486,7 @@
         <v>249</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D173" s="3" t="s">
         <v>76</v>
@@ -5953,7 +6505,7 @@
       </c>
       <c r="I173" s="3"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9">
       <c r="A174" s="3">
         <v>69867</v>
       </c>
@@ -5961,7 +6513,7 @@
         <v>250</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D174" s="3" t="s">
         <v>77</v>
@@ -5980,7 +6532,7 @@
       </c>
       <c r="I174" s="3"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9">
       <c r="A175" s="3">
         <v>75066</v>
       </c>
@@ -5988,7 +6540,7 @@
         <v>251</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D175" s="3" t="s">
         <v>78</v>
@@ -6007,7 +6559,7 @@
       </c>
       <c r="I175" s="3"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9">
       <c r="A176" s="3">
         <v>227</v>
       </c>
@@ -6015,7 +6567,7 @@
         <v>256</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D176" s="3" t="s">
         <v>83</v>
@@ -6030,11 +6582,11 @@
         <v>260</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I176" s="3"/>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:15">
       <c r="A177" s="3">
         <v>49400</v>
       </c>
@@ -6042,7 +6594,7 @@
         <v>257</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>84</v>
@@ -6057,580 +6609,5837 @@
         <v>260</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="I177" s="3"/>
     </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:15">
       <c r="N185" s="3" t="s">
         <v>267</v>
       </c>
       <c r="O185" s="1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="186" spans="1:15">
       <c r="N186" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O186" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.25">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="187" spans="1:15">
       <c r="N187" s="3" t="s">
         <v>5</v>
       </c>
       <c r="O187" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="188" spans="1:15">
       <c r="N188" s="3" t="s">
         <v>269</v>
       </c>
       <c r="O188" s="1" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="189" spans="1:15">
+      <c r="N189" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="O189" s="1" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="N189" s="3" t="s">
+    <row r="190" spans="1:15">
+      <c r="N190" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="O189" s="1" t="s">
+      <c r="O190" s="1" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="N190" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="O190" s="1" t="s">
+    <row r="191" spans="1:15">
+      <c r="N191" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="O191" s="1" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="N191" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="O191" s="1" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:15">
       <c r="N192" s="3" t="s">
         <v>268</v>
       </c>
       <c r="O192" s="1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="193" spans="14:14" x14ac:dyDescent="0.25">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="193" spans="14:14">
       <c r="N193"/>
     </row>
-    <row r="194" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="194" spans="14:14">
       <c r="N194"/>
     </row>
-    <row r="195" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="14:14">
       <c r="N195"/>
     </row>
-    <row r="196" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="196" spans="14:14">
       <c r="N196"/>
     </row>
-    <row r="197" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="197" spans="14:14">
       <c r="N197"/>
     </row>
-    <row r="198" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="14:14">
       <c r="N198"/>
     </row>
-    <row r="199" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="14:14">
       <c r="N199"/>
     </row>
-    <row r="200" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="14:14">
       <c r="N200"/>
     </row>
-    <row r="201" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="14:14">
       <c r="N201"/>
     </row>
-    <row r="202" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="14:14">
       <c r="N202"/>
     </row>
-    <row r="203" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="14:14">
       <c r="N203"/>
     </row>
-    <row r="204" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="14:14">
       <c r="N204"/>
     </row>
-    <row r="205" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="14:14">
       <c r="N205"/>
     </row>
-    <row r="206" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="206" spans="14:14">
       <c r="N206"/>
     </row>
-    <row r="207" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="14:14">
       <c r="N207"/>
     </row>
-    <row r="208" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="208" spans="14:14">
       <c r="N208"/>
     </row>
-    <row r="209" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="209" spans="14:14">
       <c r="N209"/>
     </row>
-    <row r="210" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="210" spans="14:14">
       <c r="N210"/>
     </row>
-    <row r="211" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="211" spans="14:14">
       <c r="N211"/>
     </row>
-    <row r="212" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="212" spans="14:14">
       <c r="N212"/>
     </row>
-    <row r="213" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="213" spans="14:14">
       <c r="N213"/>
     </row>
-    <row r="214" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="214" spans="14:14">
       <c r="N214"/>
     </row>
-    <row r="215" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="215" spans="14:14">
       <c r="N215"/>
     </row>
-    <row r="216" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="216" spans="14:14">
       <c r="N216"/>
     </row>
-    <row r="217" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="217" spans="14:14">
       <c r="N217"/>
     </row>
-    <row r="218" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="218" spans="14:14">
       <c r="N218"/>
     </row>
-    <row r="219" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="219" spans="14:14">
       <c r="N219"/>
     </row>
-    <row r="220" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="220" spans="14:14">
       <c r="N220"/>
     </row>
-    <row r="221" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="221" spans="14:14">
       <c r="N221"/>
     </row>
-    <row r="222" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="222" spans="14:14">
       <c r="N222"/>
     </row>
-    <row r="223" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="223" spans="14:14">
       <c r="N223"/>
     </row>
-    <row r="224" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="224" spans="14:14">
       <c r="N224"/>
     </row>
-    <row r="225" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="225" spans="14:14">
       <c r="N225"/>
     </row>
-    <row r="226" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="226" spans="14:14">
       <c r="N226"/>
     </row>
-    <row r="227" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="227" spans="14:14">
       <c r="N227"/>
     </row>
-    <row r="228" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="228" spans="14:14">
       <c r="N228"/>
     </row>
-    <row r="229" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="229" spans="14:14">
       <c r="N229"/>
     </row>
-    <row r="230" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="230" spans="14:14">
       <c r="N230"/>
     </row>
-    <row r="231" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="231" spans="14:14">
       <c r="N231"/>
     </row>
-    <row r="232" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="232" spans="14:14">
       <c r="N232"/>
     </row>
-    <row r="233" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="233" spans="14:14">
       <c r="N233"/>
     </row>
-    <row r="234" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="234" spans="14:14">
       <c r="N234"/>
     </row>
-    <row r="235" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="235" spans="14:14">
       <c r="N235"/>
     </row>
-    <row r="236" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="236" spans="14:14">
       <c r="N236"/>
     </row>
-    <row r="237" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="237" spans="14:14">
       <c r="N237"/>
     </row>
-    <row r="238" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="238" spans="14:14">
       <c r="N238"/>
     </row>
-    <row r="239" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="239" spans="14:14">
       <c r="N239"/>
     </row>
-    <row r="240" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="240" spans="14:14">
       <c r="N240"/>
     </row>
-    <row r="241" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="241" spans="14:14">
       <c r="N241"/>
     </row>
-    <row r="242" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="242" spans="14:14">
       <c r="N242"/>
     </row>
-    <row r="243" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="243" spans="14:14">
       <c r="N243"/>
     </row>
-    <row r="244" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="244" spans="14:14">
       <c r="N244"/>
     </row>
-    <row r="245" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="245" spans="14:14">
       <c r="N245"/>
     </row>
-    <row r="246" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="246" spans="14:14">
       <c r="N246"/>
     </row>
-    <row r="247" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="247" spans="14:14">
       <c r="N247"/>
     </row>
-    <row r="248" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="248" spans="14:14">
       <c r="N248"/>
     </row>
-    <row r="249" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="249" spans="14:14">
       <c r="N249"/>
     </row>
-    <row r="250" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="250" spans="14:14">
       <c r="N250"/>
     </row>
-    <row r="251" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="251" spans="14:14">
       <c r="N251"/>
     </row>
-    <row r="252" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="252" spans="14:14">
       <c r="N252"/>
     </row>
-    <row r="253" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="253" spans="14:14">
       <c r="N253"/>
     </row>
-    <row r="254" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="254" spans="14:14">
       <c r="N254"/>
     </row>
-    <row r="255" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="255" spans="14:14">
       <c r="N255"/>
     </row>
-    <row r="256" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="256" spans="14:14">
       <c r="N256"/>
     </row>
-    <row r="257" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="257" spans="14:14">
       <c r="N257"/>
     </row>
-    <row r="258" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="258" spans="14:14">
       <c r="N258"/>
     </row>
-    <row r="259" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="259" spans="14:14">
       <c r="N259"/>
     </row>
-    <row r="260" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="260" spans="14:14">
       <c r="N260"/>
     </row>
-    <row r="261" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="261" spans="14:14">
       <c r="N261"/>
     </row>
-    <row r="262" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="262" spans="14:14">
       <c r="N262"/>
     </row>
-    <row r="263" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="263" spans="14:14">
       <c r="N263"/>
     </row>
-    <row r="264" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="264" spans="14:14">
       <c r="N264"/>
     </row>
-    <row r="265" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="265" spans="14:14">
       <c r="N265"/>
     </row>
-    <row r="266" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="266" spans="14:14">
       <c r="N266"/>
     </row>
-    <row r="267" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="267" spans="14:14">
       <c r="N267"/>
     </row>
-    <row r="268" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="268" spans="14:14">
       <c r="N268"/>
     </row>
-    <row r="269" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="269" spans="14:14">
       <c r="N269"/>
     </row>
-    <row r="270" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="270" spans="14:14">
       <c r="N270"/>
     </row>
-    <row r="271" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="271" spans="14:14">
       <c r="N271"/>
     </row>
-    <row r="272" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="272" spans="14:14">
       <c r="N272"/>
     </row>
-    <row r="273" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="273" spans="14:14">
       <c r="N273"/>
     </row>
-    <row r="274" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="274" spans="14:14">
       <c r="N274"/>
     </row>
-    <row r="275" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="275" spans="14:14">
       <c r="N275"/>
     </row>
-    <row r="276" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="276" spans="14:14">
       <c r="N276"/>
     </row>
-    <row r="277" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="277" spans="14:14">
       <c r="N277"/>
     </row>
-    <row r="278" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="278" spans="14:14">
       <c r="N278"/>
     </row>
-    <row r="279" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="279" spans="14:14">
       <c r="N279"/>
     </row>
-    <row r="280" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="280" spans="14:14">
       <c r="N280"/>
     </row>
-    <row r="281" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="281" spans="14:14">
       <c r="N281"/>
     </row>
-    <row r="282" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="282" spans="14:14">
       <c r="N282"/>
     </row>
-    <row r="283" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="283" spans="14:14">
       <c r="N283"/>
     </row>
-    <row r="284" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="284" spans="14:14">
       <c r="N284"/>
     </row>
-    <row r="285" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="285" spans="14:14">
       <c r="N285"/>
     </row>
-    <row r="286" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="286" spans="14:14">
       <c r="N286"/>
     </row>
-    <row r="287" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="287" spans="14:14">
       <c r="N287"/>
     </row>
-    <row r="288" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="288" spans="14:14">
       <c r="N288"/>
     </row>
-    <row r="289" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="289" spans="14:14">
       <c r="N289"/>
     </row>
-    <row r="290" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="290" spans="14:14">
       <c r="N290"/>
     </row>
-    <row r="291" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="291" spans="14:14">
       <c r="N291"/>
     </row>
-    <row r="292" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="292" spans="14:14">
       <c r="N292"/>
     </row>
-    <row r="293" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="293" spans="14:14">
       <c r="N293"/>
     </row>
-    <row r="294" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="294" spans="14:14">
       <c r="N294"/>
     </row>
-    <row r="295" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="295" spans="14:14">
       <c r="N295"/>
     </row>
-    <row r="296" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="296" spans="14:14">
       <c r="N296"/>
     </row>
-    <row r="297" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="297" spans="14:14">
       <c r="N297"/>
     </row>
-    <row r="298" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="298" spans="14:14">
       <c r="N298"/>
     </row>
-    <row r="299" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="299" spans="14:14">
       <c r="N299"/>
     </row>
-    <row r="300" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="300" spans="14:14">
       <c r="N300"/>
     </row>
-    <row r="301" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="301" spans="14:14">
       <c r="N301"/>
     </row>
-    <row r="302" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="302" spans="14:14">
       <c r="N302"/>
     </row>
-    <row r="303" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="303" spans="14:14">
       <c r="N303"/>
     </row>
-    <row r="304" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="304" spans="14:14">
       <c r="N304"/>
     </row>
-    <row r="305" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="305" spans="14:14">
       <c r="N305"/>
     </row>
-    <row r="306" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="306" spans="14:14">
       <c r="N306"/>
     </row>
-    <row r="307" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="307" spans="14:14">
       <c r="N307"/>
     </row>
-    <row r="308" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="308" spans="14:14">
       <c r="N308"/>
     </row>
-    <row r="309" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="309" spans="14:14">
       <c r="N309"/>
     </row>
-    <row r="310" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="310" spans="14:14">
       <c r="N310"/>
     </row>
-    <row r="311" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="311" spans="14:14">
       <c r="N311"/>
     </row>
-    <row r="312" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="312" spans="14:14">
       <c r="N312"/>
     </row>
-    <row r="313" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="313" spans="14:14">
       <c r="N313"/>
     </row>
-    <row r="314" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="314" spans="14:14">
       <c r="N314"/>
     </row>
-    <row r="315" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="315" spans="14:14">
       <c r="N315"/>
     </row>
-    <row r="316" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="316" spans="14:14">
       <c r="N316"/>
     </row>
-    <row r="317" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="317" spans="14:14">
       <c r="N317"/>
     </row>
-    <row r="318" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="318" spans="14:14">
       <c r="N318"/>
     </row>
-    <row r="319" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="319" spans="14:14">
       <c r="N319"/>
     </row>
-    <row r="320" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="320" spans="14:14">
       <c r="N320"/>
     </row>
-    <row r="321" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="321" spans="14:14">
       <c r="N321"/>
     </row>
-    <row r="322" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="322" spans="14:14">
       <c r="N322"/>
     </row>
-    <row r="323" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="323" spans="14:14">
       <c r="N323"/>
     </row>
-    <row r="324" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="324" spans="14:14">
       <c r="N324"/>
     </row>
-    <row r="325" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="325" spans="14:14">
       <c r="N325"/>
     </row>
-    <row r="326" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="326" spans="14:14">
       <c r="N326"/>
     </row>
-    <row r="327" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="327" spans="14:14">
       <c r="N327"/>
     </row>
-    <row r="328" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="328" spans="14:14">
       <c r="N328"/>
     </row>
-    <row r="329" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="329" spans="14:14">
       <c r="N329"/>
     </row>
-    <row r="330" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="330" spans="14:14">
       <c r="N330"/>
     </row>
-    <row r="331" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="331" spans="14:14">
       <c r="N331"/>
     </row>
-    <row r="332" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="332" spans="14:14">
       <c r="N332"/>
     </row>
-    <row r="333" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="333" spans="14:14">
       <c r="N333"/>
     </row>
-    <row r="334" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="334" spans="14:14">
       <c r="N334"/>
     </row>
-    <row r="335" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="335" spans="14:14">
       <c r="N335"/>
     </row>
-    <row r="336" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="336" spans="14:14">
       <c r="N336"/>
     </row>
-    <row r="337" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="337" spans="14:14">
       <c r="N337"/>
     </row>
-    <row r="338" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="338" spans="14:14">
       <c r="N338"/>
     </row>
-    <row r="339" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="339" spans="14:14">
       <c r="N339"/>
     </row>
-    <row r="340" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="340" spans="14:14">
       <c r="N340"/>
     </row>
-    <row r="341" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="341" spans="14:14">
       <c r="N341"/>
     </row>
-    <row r="342" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="342" spans="14:14">
       <c r="N342"/>
     </row>
-    <row r="343" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="343" spans="14:14">
       <c r="N343"/>
     </row>
-    <row r="344" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="344" spans="14:14">
       <c r="N344"/>
     </row>
-    <row r="345" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="345" spans="14:14">
       <c r="N345"/>
     </row>
-    <row r="346" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="346" spans="14:14">
       <c r="N346"/>
     </row>
-    <row r="347" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="347" spans="14:14">
       <c r="N347"/>
     </row>
-    <row r="348" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="348" spans="14:14">
       <c r="N348"/>
     </row>
-    <row r="349" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="349" spans="14:14">
       <c r="N349"/>
     </row>
-    <row r="350" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="350" spans="14:14">
       <c r="N350"/>
     </row>
-    <row r="351" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="351" spans="14:14">
       <c r="N351"/>
     </row>
-    <row r="352" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="352" spans="14:14">
       <c r="N352"/>
     </row>
-    <row r="353" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="353" spans="14:14">
       <c r="N353"/>
     </row>
-    <row r="354" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="354" spans="14:14">
       <c r="N354"/>
     </row>
-    <row r="355" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="355" spans="14:14">
       <c r="N355"/>
     </row>
-    <row r="356" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="356" spans="14:14">
       <c r="N356"/>
     </row>
-    <row r="357" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="357" spans="14:14">
       <c r="N357"/>
     </row>
-    <row r="358" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="358" spans="14:14">
       <c r="N358"/>
     </row>
-    <row r="359" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="359" spans="14:14">
       <c r="N359"/>
     </row>
-    <row r="360" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="360" spans="14:14">
       <c r="N360"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I177" xr:uid="{A457A5FF-58BA-4FEE-9EE7-1F24D64D05BC}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E654C18-5DA2-4106-9728-176BD2813BE4}">
+  <dimension ref="A1:F328"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="E2">
+        <v>16.149999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="E3">
+        <v>16.149999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E4">
+        <v>21.36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E5">
+        <v>8.83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E6">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="E7">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E8">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E20">
+        <v>227.142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E21">
+        <v>113.571</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E22">
+        <v>113.571</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E36">
+        <v>1.635953</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E37">
+        <v>0.80396100000000004</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E38">
+        <v>0.83199199999999995</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E39">
+        <v>0.58027800000000007</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E40">
+        <v>0.18634100000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E41">
+        <v>0.18430099999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E42">
+        <v>0.20963599999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E43">
+        <v>4.6624599999999994</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E44">
+        <v>2.3348800000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E45">
+        <v>2.3275799999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="E46">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="E47">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="E48">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="E49">
+        <v>14.399999999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E50">
+        <v>146.57499999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E51">
+        <v>49.097999999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E52">
+        <v>48.844999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E53">
+        <v>48.631999999999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E58">
+        <v>23.889150000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="E59">
+        <v>8.0228199999999994</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="E60">
+        <v>7.9473599999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="E61">
+        <v>7.9189699999999998</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E62">
+        <f>E63+E64</f>
+        <v>19.966999999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="E63">
+        <v>9.9760000000000009</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E64">
+        <v>9.9909999999999997</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E65">
+        <v>9.8500000000000014</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="E66">
+        <v>4.7720000000000002</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E67">
+        <v>5.0780000000000003</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B68" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D68" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E68">
+        <v>9.9643300000000004</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="E69">
+        <v>5.0392099999999997</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E70">
+        <v>4.9251199999999997</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E71">
+        <v>19.966000000000001</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="E72">
+        <v>9.984</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E73">
+        <v>9.9819999999999993</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="E74">
+        <v>6.6360000000000001</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="E75">
+        <v>3.2989999999999999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E76">
+        <v>3.3370000000000002</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E77">
+        <v>3.262</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="E78">
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="E79">
+        <v>6.5020000000000007</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E80">
+        <v>17.462</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E81">
+        <v>29.460999999999999</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E82">
+        <v>17.41</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="E83">
+        <v>104.492</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="E84">
+        <v>168.82499999999999</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E85">
+        <v>11.090999999999999</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E86">
+        <v>11.002000000000001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E87">
+        <v>22.093</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="E88">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>364</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E89">
+        <v>10.64</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="E90">
+        <v>5.7415599999999998</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>366</v>
+      </c>
+      <c r="E91">
+        <v>5.7728700000000002</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="E92">
+        <v>5.7812900000000003</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="E93">
+        <v>5.7649600000000003</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C94" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E94">
+        <v>23.060680000000005</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E97">
+        <v>107.23099999999999</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E98">
+        <v>107.417</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E99">
+        <v>107.753</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C100" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D100" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="E100">
+        <v>108.577</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="E101">
+        <v>81.352999999999994</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="E102">
+        <v>83.787000000000006</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="E103">
+        <v>82.596000000000004</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D104" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E104">
+        <v>678.71400000000006</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="E105">
+        <v>226.47199999999998</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="E106">
+        <v>75.381</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="E107">
+        <v>75.92</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="E108">
+        <v>75.171000000000006</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="E109">
+        <v>8.8258700000000001</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B110" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="E110">
+        <v>8.5166900000000005</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="C111" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="D111" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E111">
+        <v>17.342559999999999</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B112" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E118">
+        <v>98.316000000000003</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="E119">
+        <v>49.439</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="B120" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="E120">
+        <v>48.877000000000002</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
+      <c r="A121" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
+      <c r="A122" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
+      <c r="A123" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="E123">
+        <v>88.215140000000005</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
+      <c r="A124" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="C124" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D124" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="E124">
+        <v>46.578000000000003</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
+      <c r="A125" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="E125">
+        <v>184.87493000000001</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
+      <c r="A126" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="C126" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="D126" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
+      <c r="A127" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
+      <c r="A128" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C128" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D128" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="E128">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
+      <c r="A129" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C129" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D129" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="E129">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
+      <c r="A130" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="E130">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
+      <c r="A131" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C131" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D131" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="E131">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
+      <c r="A132" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C132" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D132" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="E132">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
+      <c r="A133" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E133">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
+      <c r="A134" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B134" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="E134">
+        <v>73.599999999999994</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
+      <c r="A135" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B135" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="E135">
+        <v>37.340000000000003</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
+      <c r="A136" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="C136" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="D136" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E136">
+        <v>110.94</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
+      <c r="A137" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B137" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="C137" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="E137">
+        <v>206.49456000000001</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
+      <c r="A138" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B138" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="E138">
+        <v>206.11548999999999</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
+      <c r="A139" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B139" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="E139">
+        <v>205.99002999999999</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
+      <c r="A140" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>400</v>
+      </c>
+      <c r="C140" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="D140" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E140">
+        <v>618.60007999999993</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
+      <c r="A141" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B141" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="C141" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="D141" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E141">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
+      <c r="A142" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B142" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="D142" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E142">
+        <v>51.7</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
+      <c r="A143" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B143" s="8" t="s">
+        <v>403</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="E143">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
+      <c r="A144" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="D144" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="E144">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="A145" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="C145" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="D145" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E145">
+        <v>36.4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
+      <c r="A146" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="D146" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="E146">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
+      <c r="A147" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B147" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D147" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="A148" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D148" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="F148" s="12"/>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="A149" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B149" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C149" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D149" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
+      <c r="A150" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D150" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E150">
+        <v>495.51138000000003</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
+      <c r="A151" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="C151" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D151" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="E151">
+        <v>164.44227000000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="A152" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B152" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D152" s="10" t="s">
+        <v>457</v>
+      </c>
+      <c r="E152">
+        <v>165.47058000000001</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="A153" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B153" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="C153" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D153" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="E153">
+        <v>165.59853000000001</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
+      <c r="A154" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B154" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="C154" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D154" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E154">
+        <v>45.633629999999997</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
+      <c r="A155" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D155" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E155">
+        <v>45.615070000000003</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="A156" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B156" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="D156" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="E156">
+        <v>45.441980000000001</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="A157" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B157" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="C157" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="D157" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="E157">
+        <v>136.69067999999999</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
+      <c r="A158" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B158" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C158" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D158" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E158">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
+      <c r="A159" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B159" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C159" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D159" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="E159">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
+      <c r="A160" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B160" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C160" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D160" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="E160">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
+      <c r="A161" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B161" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C161" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D161" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="E161">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
+      <c r="A162" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B162" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
+      <c r="A163" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="B163" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="C163" s="8" t="s">
+        <v>391</v>
+      </c>
+      <c r="D163" s="8" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
+      <c r="A164" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C164" s="11" t="s">
+        <v>336</v>
+      </c>
+      <c r="D164" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="E164">
+        <v>19.768000000000001</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
+      <c r="A165" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B165" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C165" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D165" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="E165">
+        <v>9.875</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
+      <c r="A166" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B166" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="C166" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D166" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="E166">
+        <v>9.8930000000000007</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
+      <c r="A167" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B167" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C167" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D167" s="10" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
+      <c r="A168" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C168" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D168" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
+      <c r="A169" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B169" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="C169" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D169" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
+      <c r="A170" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B170" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C170" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D170" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
+      <c r="A171" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B171" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C171" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D171" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
+      <c r="A172" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B172" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="C172" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D172" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
+      <c r="A173" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D173" s="7" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
+      <c r="A174" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B174" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D174" s="7" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
+      <c r="A175" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B175" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="C175" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
+      <c r="A176" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B176" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="C176" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D176" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
+      <c r="A177" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B177" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D177" s="7" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
+      <c r="A178" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B178" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C178" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D178" s="7" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
+      <c r="A179" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B179" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C179" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D179" s="7" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
+      <c r="A180" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B180" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C180" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D180" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E180">
+        <v>582.50599999999997</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
+      <c r="A181" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B181" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C181" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D181" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E181">
+        <v>189.69200000000001</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
+      <c r="A182" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B182" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C182" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D182" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E182">
+        <v>203.053</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
+      <c r="A183" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B183" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C183" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D183" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E183">
+        <v>189.761</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
+      <c r="A184" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B184" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="C184" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D184" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E184">
+        <v>883.91</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
+      <c r="A185" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B185" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="C185" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D185" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="E185">
+        <v>182.37</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
+      <c r="A186" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B186" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="C186" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D186" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="E186">
+        <v>202.65</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
+      <c r="A187" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B187" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D187" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="E187">
+        <v>205.26</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
+      <c r="A188" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B188" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="C188" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D188" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="E188">
+        <v>293.63</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
+      <c r="A189" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B189" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="C189" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D189" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E189">
+        <v>320.2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
+      <c r="A190" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B190" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D190" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E190">
+        <v>211.16</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
+      <c r="A191" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B191" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="C191" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D191" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="E191">
+        <f>E189-E190</f>
+        <v>109.03999999999999</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
+      <c r="A192" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B192" s="7" t="s">
+        <v>426</v>
+      </c>
+      <c r="C192" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D192" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E192">
+        <v>10.83</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
+      <c r="A193" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B193" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="C193" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="D193" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E193">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
+      <c r="A194" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B194" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="C194" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="D194" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="E194">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
+      <c r="A195" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B195" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="C195" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="D195" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
+      <c r="A196" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B196" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C196" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D196" s="7" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
+      <c r="A197" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B197" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C197" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D197" s="7" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
+      <c r="A198" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B198" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="C198" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="D198" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
+      <c r="A199" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B199" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C199" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D199" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
+      <c r="A200" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B200" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C200" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D200" s="10" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
+      <c r="A201" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B201" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="C201" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D201" s="10" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
+      <c r="A202" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B202" s="11" t="s">
+        <v>475</v>
+      </c>
+      <c r="C202" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D202" s="10" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
+      <c r="A203" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B203" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C203" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D203" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E203">
+        <v>44.219000000000001</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
+      <c r="A204" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B204" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C204" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D204" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E204">
+        <v>44.552999999999997</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
+      <c r="A205" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B205" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C205" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D205" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E205">
+        <v>43.765000000000001</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
+      <c r="A206" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B206" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C206" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D206" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="E206">
+        <v>44.12</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
+      <c r="A207" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B207" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C207" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D207" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="E207">
+        <v>44.686999999999998</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
+      <c r="A208" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B208" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C208" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D208" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="E208">
+        <v>44.220999999999997</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
+      <c r="A209" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B209" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C209" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D209" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E209">
+        <v>265.565</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
+      <c r="A210" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B210" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C210" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D210" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E210">
+        <v>31.593</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
+      <c r="A211" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B211" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C211" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D211" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E211">
+        <v>31.472000000000001</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
+      <c r="A212" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B212" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C212" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D212" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E212">
+        <v>31.466999999999999</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
+      <c r="A213" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B213" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C213" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D213" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E213">
+        <v>94.531999999999996</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
+      <c r="A214" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B214" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="C214" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D214" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E214">
+        <v>9.98</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
+      <c r="A215" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B215" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="C215" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D215" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="E215">
+        <v>9.98</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
+      <c r="A216" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B216" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C216" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D216" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E216">
+        <v>16.760000000000002</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
+      <c r="A217" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B217" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C217" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D217" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E217">
+        <v>16.545000000000002</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
+      <c r="A218" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B218" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C218" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D218" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E218">
+        <v>16.587</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
+      <c r="A219" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B219" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C219" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D219" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="E219">
+        <v>34.482999999999997</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
+      <c r="A220" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B220" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="C220" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D220" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="E220">
+        <v>84.375</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
+      <c r="A221" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B221" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="C221" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="D221" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
+      <c r="A222" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B222" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="C222" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="D222" s="7" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
+      <c r="A223" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B223" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C223" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D223" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="E223">
+        <f>E224+E225</f>
+        <v>0.678643</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
+      <c r="A224" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B224" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C224" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D224" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E224">
+        <v>0.34154899999999999</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
+      <c r="A225" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B225" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="C225" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D225" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="E225">
+        <v>0.337094</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
+      <c r="A226" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B226" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="C226" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D226" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E226">
+        <v>30.85</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
+      <c r="A227" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B227" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="C227" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D227" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E227">
+        <v>15.615</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
+      <c r="A228" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B228" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="C228" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D228" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E228">
+        <v>15.234999999999999</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
+      <c r="A229" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B229" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C229" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D229" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E229">
+        <v>277.89999999999998</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
+      <c r="A230" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B230" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C230" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D230" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E230">
+        <v>69.53</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
+      <c r="A231" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B231" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C231" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D231" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E231">
+        <v>69.11</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
+      <c r="A232" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B232" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C232" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D232" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E232">
+        <v>69.914000000000001</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
+      <c r="A233" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B233" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="C233" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D233" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="E233">
+        <v>69.346000000000004</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
+      <c r="A234" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B234" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C234" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D234" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E234">
+        <v>137.02196000000001</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
+      <c r="A235" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B235" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C235" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D235" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E235">
+        <v>68.555549999999997</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
+      <c r="A236" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B236" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C236" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D236" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E236">
+        <v>68.46641000000001</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
+      <c r="A237" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B237" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C237" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D237" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E237">
+        <v>69.147999999999996</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
+      <c r="A238" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B238" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C238" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D238" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E238">
+        <v>23.824000000000002</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
+      <c r="A239" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B239" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C239" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D239" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E239">
+        <v>22.574999999999999</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
+      <c r="A240" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B240" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C240" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D240" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E240">
+        <v>22.748999999999999</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
+      <c r="A241" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B241" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="C241" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D241" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="E241">
+        <v>118.14735</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
+      <c r="A242" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B242" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="C242" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D242" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="E242">
+        <v>52.418509999999998</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
+      <c r="A243" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B243" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="C243" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D243" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="E243">
+        <v>53.710120000000003</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
+      <c r="A244" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B244" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="C244" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D244" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="E244">
+        <v>191.19621000000001</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
+      <c r="A245" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B245" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="C245" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D245" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E245">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
+      <c r="A246" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B246" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="C246" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D246" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="E246" s="9">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
+      <c r="A247" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B247" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="C247" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D247" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="E247">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
+      <c r="A248" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B248" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="C248" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D248" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="E248">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
+      <c r="A249" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B249" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="C249" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="D249" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E249">
+        <v>144.47999999999999</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
+      <c r="A250" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B250" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="C250" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="D250" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E250">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
+      <c r="A251" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B251" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="C251" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="D251" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="E251">
+        <v>132.30000000000001</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
+      <c r="A252" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B252" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="C252" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="D252" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="E252">
+        <v>114.93</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
+      <c r="A253" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B253" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="C253" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="D253" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
+      <c r="A254" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B254" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="C254" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="D254" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
+      <c r="A255" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B255" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="C255" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="D255" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E255">
+        <v>1.9571499999999999</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
+      <c r="A256" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B256" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="C256" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D256" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="E256">
+        <v>0.98250999999999999</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
+      <c r="A257" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B257" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="C257" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D257" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="E257">
+        <v>0.97463999999999995</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
+      <c r="A258" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B258" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="C258" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D258" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="E258">
+        <v>0.95943000000000001</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
+      <c r="A259" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B259" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="C259" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D259" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="E259">
+        <v>0.96914</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
+      <c r="A260" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B260" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="C260" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="D260" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="E260">
+        <v>1.9285700000000001</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
+      <c r="A261" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B261" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C261" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="D261" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="E261">
+        <v>4.4530099999999999</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
+      <c r="A262" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B262" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C262" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D262" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E262">
+        <v>1.4816400000000001</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
+      <c r="A263" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B263" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C263" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D263" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E263">
+        <v>1.4838899999999999</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
+      <c r="A264" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B264" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C264" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D264" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="E264">
+        <v>1.4874799999999999</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
+      <c r="A265" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B265" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="C265" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="D265" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="E265">
+        <v>2.9172799999999999</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
+      <c r="A266" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B266" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="C266" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D266" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E266">
+        <v>1.45967</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
+      <c r="A267" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B267" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="C267" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D267" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="E267">
+        <v>1.4576100000000001</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
+      <c r="A268" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B268" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="C268" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D268" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
+      <c r="A269" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B269" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="C269" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D269" s="7" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
+      <c r="A270" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B270" s="7" t="s">
+        <v>452</v>
+      </c>
+      <c r="C270" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D270" s="7" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B271" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="C271" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="D271" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B272" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="C272" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D272" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4">
+      <c r="A273" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B273" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="C273" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D273" s="7" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4">
+      <c r="A274" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B274" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="C274" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D274" s="7" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4">
+      <c r="A275" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B275" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="C275" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D275" s="7" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4">
+      <c r="A276" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B276" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="C276" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D276" s="7" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4">
+      <c r="A277" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B277" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="C277" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D277" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4">
+      <c r="A278" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B278" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="C278" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D278" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4">
+      <c r="A279" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B279" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="C279" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D279" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4">
+      <c r="A280" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B280" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="C280" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D280" s="7" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4">
+      <c r="A281" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B281" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="C281" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D281" s="7" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4">
+      <c r="A282" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B282" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="C282" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="D282" s="8" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4">
+      <c r="A283" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="B283" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="C283" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D283" s="7" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4">
+      <c r="A284" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="B284" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C284" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D284" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4">
+      <c r="A285" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="B285" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="C285" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D285" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4">
+      <c r="A286" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B286" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C286" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D286" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4">
+      <c r="A287" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B287" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C287" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D287" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4">
+      <c r="A288" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B288" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C288" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D288" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4">
+      <c r="A289" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B289" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C289" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D289" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4">
+      <c r="A290" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B290" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="C290" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D290" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4">
+      <c r="A291" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B291" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="C291" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D291" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4">
+      <c r="A292" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B292" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C292" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D292" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4">
+      <c r="A293" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B293" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C293" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D293" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4">
+      <c r="A294" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B294" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C294" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D294" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4">
+      <c r="A295" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B295" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C295" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D295" s="7" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4">
+      <c r="A296" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B296" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C296" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D296" s="7" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4">
+      <c r="A297" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B297" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="C297" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D297" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4">
+      <c r="A298" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B298" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="C298" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D298" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4">
+      <c r="A299" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B299" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C299" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D299" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4">
+      <c r="A300" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B300" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C300" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D300" s="7" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4">
+      <c r="A301" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B301" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C301" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D301" s="7" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4">
+      <c r="A302" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B302" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C302" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D302" s="7" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4">
+      <c r="A303" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B303" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="C303" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D303" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4">
+      <c r="A304" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B304" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="C304" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="D304" s="8" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
+      <c r="A305" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B305" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="C305" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D305" s="7" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5">
+      <c r="A306" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B306" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="C306" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D306" s="7" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5">
+      <c r="A307" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B307" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C307" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D307" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
+      <c r="A308" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B308" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C308" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="D308" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5">
+      <c r="A309" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B309" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C309" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D309" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5">
+      <c r="A310" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B310" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="C310" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D310" s="7" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5">
+      <c r="A311" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B311" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C311" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D311" s="7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5">
+      <c r="A312" t="s">
+        <v>65</v>
+      </c>
+      <c r="B312" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="C312" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D312" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="E312">
+        <v>4.6885700000000003</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5">
+      <c r="A313" t="s">
+        <v>65</v>
+      </c>
+      <c r="B313" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="C313" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D313" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="E313">
+        <v>4.3913000000000002</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
+      <c r="A314" t="s">
+        <v>65</v>
+      </c>
+      <c r="B314" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="C314" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="D314" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="E314">
+        <f>SUM(E312:E313)</f>
+        <v>9.0798699999999997</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5">
+      <c r="A315" t="s">
+        <v>65</v>
+      </c>
+      <c r="B315" t="s">
+        <v>225</v>
+      </c>
+      <c r="C315" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D315" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="E315">
+        <v>10.00642</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
+      <c r="A316" t="s">
+        <v>65</v>
+      </c>
+      <c r="B316" t="s">
+        <v>225</v>
+      </c>
+      <c r="C316" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D316" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="E316">
+        <v>10.04447</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5">
+      <c r="A317" t="s">
+        <v>65</v>
+      </c>
+      <c r="B317" t="s">
+        <v>225</v>
+      </c>
+      <c r="C317" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="D317" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="E317">
+        <v>20.050890000000003</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5">
+      <c r="A318" t="s">
+        <v>65</v>
+      </c>
+      <c r="B318" t="s">
+        <v>226</v>
+      </c>
+      <c r="C318" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D318" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="E318">
+        <v>10.02079</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5">
+      <c r="A319" t="s">
+        <v>65</v>
+      </c>
+      <c r="B319" t="s">
+        <v>226</v>
+      </c>
+      <c r="C319" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D319" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="E319">
+        <v>9.9663799999999991</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5">
+      <c r="A320" t="s">
+        <v>65</v>
+      </c>
+      <c r="B320" t="s">
+        <v>226</v>
+      </c>
+      <c r="C320" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="D320" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="E320">
+        <v>19.987169999999999</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5">
+      <c r="A321" t="s">
+        <v>65</v>
+      </c>
+      <c r="B321" t="s">
+        <v>227</v>
+      </c>
+      <c r="C321" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D321" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="E321">
+        <v>10.08095</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5">
+      <c r="A322" t="s">
+        <v>65</v>
+      </c>
+      <c r="B322" t="s">
+        <v>227</v>
+      </c>
+      <c r="C322" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D322" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="E322">
+        <v>10.00311</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
+      <c r="A323" t="s">
+        <v>65</v>
+      </c>
+      <c r="B323" t="s">
+        <v>227</v>
+      </c>
+      <c r="C323" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="D323" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="E323">
+        <v>20.084060000000001</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5">
+      <c r="A324" t="s">
+        <v>50</v>
+      </c>
+      <c r="B324" t="s">
+        <v>198</v>
+      </c>
+      <c r="C324" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D324" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="E324">
+        <v>3.9729999999999999</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5">
+      <c r="A325" t="s">
+        <v>50</v>
+      </c>
+      <c r="B325" t="s">
+        <v>198</v>
+      </c>
+      <c r="C325" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="D325" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="E325">
+        <v>3.9729999999999999</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
+      <c r="A326" t="s">
+        <v>45</v>
+      </c>
+      <c r="B326" t="s">
+        <v>193</v>
+      </c>
+      <c r="C326" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="D326" s="13" t="s">
+        <v>332</v>
+      </c>
+      <c r="E326">
+        <v>3.6848800000000002</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5">
+      <c r="A327" t="s">
+        <v>45</v>
+      </c>
+      <c r="B327" t="s">
+        <v>193</v>
+      </c>
+      <c r="C327" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D327" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="E327">
+        <v>1.8224400000000001</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5">
+      <c r="A328" t="s">
+        <v>45</v>
+      </c>
+      <c r="B328" t="s">
+        <v>193</v>
+      </c>
+      <c r="C328" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="D328" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="E328">
+        <v>1.8624400000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E309" xr:uid="{1E654C18-5DA2-4106-9728-176BD2813BE4}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>